--- a/test_perspective_analysis_with_2_new_specs.xlsx
+++ b/test_perspective_analysis_with_2_new_specs.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TaiLieu\Testing\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3CB948-E00E-4795-BD89-5022CA7A66C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDA1635-1076-44D8-B573-70851764BEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="550" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="550" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Password strength checker" sheetId="1" r:id="rId1"/>
     <sheet name="Unit converter" sheetId="2" r:id="rId2"/>
     <sheet name="Budget planner" sheetId="3" r:id="rId3"/>
-    <sheet name="Task manager" sheetId="5" r:id="rId4"/>
-    <sheet name="Library fine calculator" sheetId="6" r:id="rId5"/>
+    <sheet name="Library fine calculator" sheetId="6" r:id="rId4"/>
+    <sheet name="Task manager" sheetId="5" r:id="rId5"/>
     <sheet name="minutes for manual test design" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1257,6 +1257,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1363,7 +1370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1505,60 +1512,14 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <fill>
         <patternFill>
@@ -3481,57 +3442,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A17:B37 A2:B15 G2:O13 E17:O37 E14:O15">
-    <cfRule type="expression" dxfId="38" priority="12">
+    <cfRule type="expression" dxfId="31" priority="12">
       <formula>$P2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:B16 G16:N16 E16">
-    <cfRule type="expression" dxfId="37" priority="14">
+    <cfRule type="expression" dxfId="30" priority="14">
       <formula>$O16=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="expression" dxfId="36" priority="11">
+    <cfRule type="expression" dxfId="29" priority="11">
       <formula>$P16=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F13">
-    <cfRule type="expression" dxfId="35" priority="10">
+    <cfRule type="expression" dxfId="28" priority="10">
       <formula>$P2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:D41">
-    <cfRule type="expression" dxfId="34" priority="9">
+    <cfRule type="expression" dxfId="27" priority="9">
       <formula>$O24=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C5 C8:C13">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="26" priority="4">
       <formula>$O2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D2 D3:D13">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="25" priority="5">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C7">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="24" priority="6">
       <formula>$O4=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D24">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>$O14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D24">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$O13=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4871,32 +4832,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:O8 E11:O30 A2:B30 G9:O10 G4:H4 G8:H8 G5:G7 G2:O3">
-    <cfRule type="expression" dxfId="31" priority="14">
+    <cfRule type="expression" dxfId="20" priority="14">
       <formula>$P2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="expression" dxfId="30" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$P5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="expression" dxfId="29" priority="13">
+    <cfRule type="expression" dxfId="18" priority="13">
       <formula>$P5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="17" priority="12">
       <formula>$P6=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F10">
-    <cfRule type="expression" dxfId="27" priority="11">
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>$P2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:D41">
-    <cfRule type="expression" dxfId="26" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>$O20=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4921,17 +4882,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D20">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>$O14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D20">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C14">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$O10=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4951,8 +4912,8 @@
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="3.88671875" customWidth="1"/>
     <col min="7" max="7" width="3.109375" customWidth="1"/>
-    <col min="8" max="8" width="3.77734375" customWidth="1"/>
-    <col min="9" max="9" width="2.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
     <col min="10" max="13" width="4.109375" customWidth="1"/>
     <col min="14" max="14" width="21.33203125" customWidth="1"/>
   </cols>
@@ -6581,37 +6542,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:B41 G3:M14 E15:M41">
-    <cfRule type="expression" dxfId="23" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B2 G2:M2">
-    <cfRule type="expression" dxfId="22" priority="12">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F2 F3:F14">
-    <cfRule type="expression" dxfId="21" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E14">
-    <cfRule type="expression" dxfId="20" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D16 C29:D41">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>$N14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D2 D3:D14">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C14">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6626,1158 +6587,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36.33203125" customWidth="1"/>
-    <col min="2" max="2" width="76.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="3.44140625" customWidth="1"/>
-    <col min="9" max="13" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="10">
-        <v>2</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="9">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="11">
-        <v>1</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-    </row>
-    <row r="5" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="11">
-        <v>4</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="10">
-        <v>18</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="11">
-        <v>17</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C7" s="9">
-        <v>11</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-    </row>
-    <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="9">
-        <v>12</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="10">
-        <v>22</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="11">
-        <v>19</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-    </row>
-    <row r="9" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="9">
-        <v>13</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="10">
-        <v>19</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-    </row>
-    <row r="10" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="15">
-        <v>22</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="14">
-        <v>4</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="15">
-        <v>23</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="16">
-        <v>10</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="14">
-        <v>5</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="15">
-        <v>26</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="16">
-        <v>12</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-    </row>
-    <row r="13" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="15">
-        <v>28</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="16">
-        <v>13</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="15">
-        <v>30</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-    </row>
-    <row r="15" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="18">
-        <v>32</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="18">
-        <v>36</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="C17" s="14">
-        <v>59</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16">
-        <v>26</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-    </row>
-    <row r="18" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="18">
-        <v>42</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="21">
-        <v>34</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16">
-        <v>28</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-    </row>
-    <row r="21" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="45" t="s">
-        <v>389</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-    </row>
-    <row r="22" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="C22" s="25">
-        <v>36</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>386</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="45" t="s">
-        <v>388</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-    </row>
-    <row r="23" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>390</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="45" t="s">
-        <v>391</v>
-      </c>
-      <c r="H25" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-    </row>
-    <row r="26" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-    </row>
-    <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="26">
-        <v>24</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="H28" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-    </row>
-    <row r="29" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="25">
-        <v>31</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="26">
-        <v>20</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="27">
-        <v>53</v>
-      </c>
-      <c r="H29" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-    </row>
-    <row r="30" spans="1:13" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="F30" s="26"/>
-      <c r="G30" s="27">
-        <v>61</v>
-      </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7822,7 +6631,7 @@
       <c r="H1" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="47" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -7838,7 +6647,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>252</v>
       </c>
@@ -8055,7 +6864,7 @@
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
     </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>252</v>
       </c>
@@ -8694,6 +7503,1161 @@
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="76.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.21875" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" customWidth="1"/>
+    <col min="11" max="11" width="7.21875" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="11">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="9">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="11">
+        <v>4</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="10">
+        <v>18</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="11">
+        <v>17</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="9">
+        <v>11</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="9">
+        <v>12</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="10">
+        <v>22</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="11">
+        <v>19</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+    </row>
+    <row r="9" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="9">
+        <v>13</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="10">
+        <v>19</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="15">
+        <v>22</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="14">
+        <v>4</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="15">
+        <v>23</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="16">
+        <v>10</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="14">
+        <v>5</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="15">
+        <v>26</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="16">
+        <v>12</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="15">
+        <v>28</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="16">
+        <v>13</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="15">
+        <v>30</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="18">
+        <v>32</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="18">
+        <v>36</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="14">
+        <v>59</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16">
+        <v>26</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="18">
+        <v>42</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="21">
+        <v>34</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="16">
+        <v>28</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="25">
+        <v>36</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>388</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="45" t="s">
+        <v>391</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="F27" s="26"/>
+      <c r="G27" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" s="27"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="26">
+        <v>24</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" s="25">
+        <v>31</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="26">
+        <v>20</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="27">
+        <v>53</v>
+      </c>
+      <c r="H29" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30" spans="1:13" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27">
+        <v>61</v>
+      </c>
+      <c r="H30" s="27"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
